--- a/data/output/evaluasi_82.xlsx
+++ b/data/output/evaluasi_82.xlsx
@@ -8,14 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="8200" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="8201" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="8206" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="8202" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="8203" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="8203" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="8202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="8204" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="8205" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="8207" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="8208" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8271" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8271" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8206" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="8272" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="8208" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="8201" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,20 +481,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.103856323603228</v>
+        <v>16.48337470123486</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q2-25</t>
+          <t>adhb_pkp_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -507,20 +509,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.2421620462707706</v>
+        <v>184.9662090067597</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -535,20 +537,1820 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-9.25180894566647</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>18.87770454451893</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhk_pkp_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>48.3268848781943</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>adhk_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.639631851904734</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>82</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.382887933971363</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25 vs q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>82</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.9416834624326375</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q1-25 vs q-to-q_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
+      <c r="D10" t="n">
+        <v>1.787535047923577</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q2-25 vs q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>82</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-4.966400691139194</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25 vs q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>82</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>21.83995046900513</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>82</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-12.26098305238806</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>82</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>21.73596081795793</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>82</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>39.87043356467306</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>82</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6.138408319597135</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q1-25 vs y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>82</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.923212506094258</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>82</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8.375876059777285</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>82</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.134413099661172</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>82</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-20.41284585746254</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>82</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>16.55743591028868</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>82</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>37.20534046108821</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>82</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6.138408319597135</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q1-25 vs c-to-c_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>82</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8.375876059777285</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>82</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-6.365122582556992</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>82</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>16.55743591028868</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>82</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>23.67635317615462</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25 vs c-to-c_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>82</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3.339434938284293</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q2-25 vs implisit_q-to-q_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>82</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1.161663808383386</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25 vs implisit_q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>82</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.013374204274538</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25 vs implisit_q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>82</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.7616058055476118</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>82</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1.600158749099788</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>82</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Maluku Utara</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2.198714233208158</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.961983026166359</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.082301121360651</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
       <c r="D4" t="n">
-        <v>1.600158749105902</v>
+        <v>-8.00172485307332</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-77.57146841483393</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>26.14954746291254</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>40.73956699930385</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.121088151752905</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.104856293409549</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-78.76260997244074</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20.8431400254794</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-50.82310680489321</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.917654232358598</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-29.06879346222994</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-8.453463507041816</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-42.98977505355111</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-10.01272578593845</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-6.171691743791186</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-7.901825022483767</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2.099554130736898</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.222518867310567</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-14.42010346030823</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>39.97540883299822</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.596926974658186</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-12.64496509045002</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-8.393421194796979</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.497449549185949</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-5.418293793589048</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-9.872870868869331</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8602520013937609</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1096946377039311</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.572878397903828</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.037581227564164</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -563,7 +2365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,151 +2402,151 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>38749.96822754336</v>
+        <v>53721.4864704</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>adhb_net_ekspor_q2-25_ril vs adhb_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-3950.116295459142</v>
+        <v>-11257.5661561</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>adhk_net_ekspor_q2-25_ril vs adhk_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5609558454205128</v>
+        <v>136.4698563047809</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q2-25_ril vs q-to-q_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02767043450874051</v>
+        <v>-23.18535454762604</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pmtb_q2-25_ril vs y-on-y_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-4.753908183220765</v>
+        <v>-22.96478418522945</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pmtb_q2-25_ril vs c-to-c_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -753,26 +2555,26 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.192337335798402</v>
+        <v>6.153985608545035</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -781,212 +2583,408 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.02767043450874051</v>
+        <v>-2.12284809030863</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-4.753908183220765</v>
+        <v>12.36722978295776</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-3.192337335798402</v>
+        <v>19.88756042120691</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.116375001812854</v>
+        <v>160.2750834362783</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02621142109471882</v>
+        <v>7.905017549614618</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.001363670626795682</v>
+        <v>19.56968718467562</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.199601995190059</v>
+        <v>21.2298272802971</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8201</v>
+        <v>8203</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Barat</t>
+          <t>Kabupaten Kepulauan Sula</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.2002988624938794</v>
+        <v>0.5301330120929428</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>74.77060636809509</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6.346757946427176</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>9.585555395095611</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q3-25_prov vs c-to-c_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5.990361182100544</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6.464694577503753</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.5829502291040434</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.382880337533228</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1001,7 +2999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1038,11 +3036,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Timur</t>
+          <t>Kabupaten Halmahera Tengah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,26 +3049,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>270021.9888618719</v>
+        <v>2.356650416536941</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Timur</t>
+          <t>Kabupaten Halmahera Tengah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1079,184 +3077,296 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.752535056386678</v>
+        <v>-6.118307027813573</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>q-to-q_pdrb_q1-25_ril vs q-to-q_pdrb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Timur</t>
+          <t>Kabupaten Halmahera Tengah</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.465703141220082</v>
+        <v>-4.506387991327134</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Timur</t>
+          <t>Kabupaten Halmahera Tengah</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.226344451216088</v>
+        <v>94.52667949348169</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Timur</t>
+          <t>Kabupaten Halmahera Tengah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.226344451216088</v>
+        <v>-24.88528118486352</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Timur</t>
+          <t>Kabupaten Halmahera Tengah</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.752535056386678</v>
+        <v>51.4454072295086</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_q_pdrb_q1-25_ril vs sog_q_pdrb_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Timur</t>
+          <t>Kabupaten Halmahera Tengah</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02851292122832949</v>
+        <v>74.37245826597824</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Timur</t>
+          <t>Kabupaten Halmahera Tengah</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.02743549816258172</v>
+        <v>6.661500396773497</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>38.57669159733337</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.862786261418758</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.662402362079747</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.940267594996992</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1271,7 +3381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,11 +3418,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Tengah</t>
+          <t>Kabupaten Halmahera Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1321,26 +3431,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.082396966847387</v>
+        <v>-4.325240095024264</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Tengah</t>
+          <t>Kabupaten Halmahera Selatan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1349,156 +3459,184 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.30890048349327</v>
+        <v>-5.284953444222428</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>q-to-q_pmtb_q1-25_ril vs q-to-q_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Tengah</t>
+          <t>Kabupaten Halmahera Selatan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.02014533534917</v>
+        <v>-2.896638980935967</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Tengah</t>
+          <t>Kabupaten Halmahera Selatan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.02014533534917</v>
+        <v>31.64910940017474</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Tengah</t>
+          <t>Kabupaten Halmahera Selatan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.001155152430212524</v>
+        <v>-10.31796878452784</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Tengah</t>
+          <t>Kabupaten Halmahera Selatan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.881867280440635</v>
+        <v>47.45794064899756</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_q_pmtb_q1-25_ril vs sog_q_pmtb_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Halmahera Tengah</t>
+          <t>Kabupaten Halmahera Selatan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.001932808104716783</v>
+        <v>16.27786955001701</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3362065170900481</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1513,7 +3651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,11 +3688,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8203</v>
+        <v>8205</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Sula</t>
+          <t>Kabupaten Halmahera Utara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1563,54 +3701,54 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.487404717501362</v>
+        <v>4.509401739846043</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8203</v>
+        <v>8205</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Sula</t>
+          <t>Kabupaten Halmahera Utara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.631676701320308</v>
+        <v>-2.793588776995675</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8203</v>
+        <v>8205</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Sula</t>
+          <t>Kabupaten Halmahera Utara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1619,72 +3757,352 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.631676701320308</v>
+        <v>-2.799890555762428</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8203</v>
+        <v>8205</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Sula</t>
+          <t>Kabupaten Halmahera Utara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.01238126011517716</v>
+        <v>-4.262713653366569</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8203</v>
+        <v>8205</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Sula</t>
+          <t>Kabupaten Halmahera Utara</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.0147278222642963</v>
+        <v>0.7482270889146629</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2366332229816522</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8.929281261938952</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.878962868912322</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.967031988074925</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>24.25214304530985</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.508491037237132</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.263104538064589</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16.16083184728194</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.244788909618116</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.976250425612674</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1699,7 +4117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1749,16 +4167,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.759618701621875</v>
+        <v>4.673389920086595</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1773,20 +4191,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.312062073769038</v>
+        <v>-2.198884016778164</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1805,16 +4223,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.312062073769038</v>
+        <v>-2.215761125748057</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1829,20 +4247,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.01014151752513032</v>
+        <v>-2.176308620977707</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1857,20 +4275,300 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.007888078925554588</v>
+        <v>9.911077171831932</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-14.03945976821331</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.869568803610007</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-25.66409706666977</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-66.2575852324472</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.111248091122522</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-10.95595238887901</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-38.15092615148045</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8934672621779269</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.361206736394991</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.4969244146057235</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1885,7 +4583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,11 +4620,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8208</v>
+        <v>8271</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pulau Taliabu</t>
+          <t>Kota Ternate</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1935,54 +4633,54 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.631000784114171</v>
+        <v>2.491996510959194</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8208</v>
+        <v>8271</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Pulau Taliabu</t>
+          <t>Kota Ternate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.754355072355665</v>
+        <v>-3.903036932593678</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8208</v>
+        <v>8271</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Pulau Taliabu</t>
+          <t>Kota Ternate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1991,72 +4689,296 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.754355072355665</v>
+        <v>-2.664396555791408</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8208</v>
+        <v>8271</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Pulau Taliabu</t>
+          <t>Kota Ternate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.003967704837832009</v>
+        <v>-0.6945044875144378</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8208</v>
+        <v>8271</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Pulau Taliabu</t>
+          <t>Kota Ternate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.004422136288683701</v>
+        <v>-31.45444759482605</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.839915099998446</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.7289426691535</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-33.95108477958022</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-41.06295828517396</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.199304915870189</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-13.2947625809751</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-25.22103114271329</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.032569440260414</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2071,7 +4993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2108,39 +5030,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8271</v>
+        <v>8206</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Ternate</t>
+          <t>Kabupaten Halmahera Timur</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.005172299267110696</v>
+        <v>-4.294070243710168</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8271</v>
+        <v>8206</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Ternate</t>
+          <t>Kabupaten Halmahera Timur</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2149,128 +5071,352 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.154828329803681</v>
+        <v>-2.667496775209129</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8271</v>
+        <v>8206</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Ternate</t>
+          <t>Kabupaten Halmahera Timur</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.154828329803681</v>
+        <v>-6.001739166824863</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8271</v>
+        <v>8206</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kota Ternate</t>
+          <t>Kabupaten Halmahera Timur</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07315176115142444</v>
+        <v>-4.886805701670577</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8271</v>
+        <v>8206</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kota Ternate</t>
+          <t>Kabupaten Halmahera Timur</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.392106919968076e-05</v>
+        <v>-8.043900849579789</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8271</v>
+        <v>8206</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kota Ternate</t>
+          <t>Kabupaten Halmahera Timur</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.002076293584374462</v>
+        <v>88.0268310794857</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>49.32025866173877</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-38.62717881472874</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>46.51592063281706</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-12.59655446317728</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.08738969450140639</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.931613950750813</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.85668800278317</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.825271385009418</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2285,7 +5431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2331,20 +5477,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.720061873334595</v>
+        <v>-2.307223578607664</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2363,16 +5509,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.767171425963074</v>
+        <v>-2.379049853928124</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2387,20 +5533,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.767171425963074</v>
+        <v>-2.98897795852085</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2415,20 +5561,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05092520856936319</v>
+        <v>-16.17058187014096</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2443,20 +5589,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05604453401098134</v>
+        <v>119.3342481250952</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.421912467848312</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-9.77010644180168</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-30.50792752743104</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.773873558191258</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-7.67388503032632</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-38.63522385636015</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4685636330663052</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.685954378558909</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_82.xlsx
+++ b/data/output/evaluasi_82.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
